--- a/artifacts/ui-audit/SN318_UI规范审查_测试建议与修改清单.xlsx
+++ b/artifacts/ui-audit/SN318_UI规范审查_测试建议与修改清单.xlsx
@@ -4495,7 +4495,7 @@
         <x:v>历史观察需在本批复核</x:v>
       </x:c>
       <x:c r="E30" s="20" t="str">
-        <x:v>thread://smoke-ui?hostId=local</x:v>
+        <x:v>https://example.invalid/local-reference</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
